--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG173"/>
+  <dimension ref="A1:AI173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,16 @@
         </is>
       </c>
       <c r="AG1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
@@ -658,7 +668,17 @@
           <t>010201</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>UGEL BAGUA</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -735,7 +755,17 @@
           <t>020101</t>
         </is>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -814,7 +844,17 @@
           <t>020801</t>
         </is>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -893,7 +933,17 @@
           <t>021801</t>
         </is>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -970,7 +1020,17 @@
           <t>021809</t>
         </is>
       </c>
-      <c r="AG6" t="n">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1047,7 +1107,17 @@
           <t>030101</t>
         </is>
       </c>
-      <c r="AG7" t="n">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1124,7 +1194,17 @@
           <t>030104</t>
         </is>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1201,7 +1281,17 @@
           <t>030201</t>
         </is>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1280,7 +1370,17 @@
           <t>030701</t>
         </is>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1359,7 +1459,17 @@
           <t>030712</t>
         </is>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1436,7 +1546,17 @@
           <t>040101</t>
         </is>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1513,7 +1633,17 @@
           <t>040102</t>
         </is>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1590,7 +1720,17 @@
           <t>040103</t>
         </is>
       </c>
-      <c r="AG14" t="n">
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI14" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1667,7 +1807,17 @@
           <t>040105</t>
         </is>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1744,7 +1894,17 @@
           <t>040110</t>
         </is>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1821,7 +1981,17 @@
           <t>040112</t>
         </is>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1898,7 +2068,17 @@
           <t>040129</t>
         </is>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1977,7 +2157,17 @@
           <t>040201</t>
         </is>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2054,7 +2244,17 @@
           <t>040701</t>
         </is>
       </c>
-      <c r="AG20" t="n">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>UGEL ISLAY</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2133,7 +2333,17 @@
           <t>050405</t>
         </is>
       </c>
-      <c r="AG21" t="n">
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2210,7 +2420,17 @@
           <t>050601</t>
         </is>
       </c>
-      <c r="AG22" t="n">
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2287,7 +2507,17 @@
           <t>240304</t>
         </is>
       </c>
-      <c r="AG23" t="n">
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2364,7 +2594,17 @@
           <t>060108</t>
         </is>
       </c>
-      <c r="AG24" t="n">
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2443,7 +2683,17 @@
           <t>060401</t>
         </is>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2520,7 +2770,17 @@
           <t>060901</t>
         </is>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2599,7 +2859,17 @@
           <t>070102</t>
         </is>
       </c>
-      <c r="AG27" t="n">
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2676,7 +2946,17 @@
           <t>070103</t>
         </is>
       </c>
-      <c r="AG28" t="n">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2753,7 +3033,17 @@
           <t>070104</t>
         </is>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2832,7 +3122,17 @@
           <t>080101</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2911,7 +3211,17 @@
           <t>080104</t>
         </is>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2988,7 +3298,17 @@
           <t>080401</t>
         </is>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3065,7 +3385,17 @@
           <t>080601</t>
         </is>
       </c>
-      <c r="AG33" t="n">
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3144,7 +3474,17 @@
           <t>080801</t>
         </is>
       </c>
-      <c r="AG34" t="n">
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
+      <c r="AI34" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3223,7 +3563,17 @@
           <t>090101</t>
         </is>
       </c>
-      <c r="AG35" t="n">
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AI35" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3302,7 +3652,17 @@
           <t>040201</t>
         </is>
       </c>
-      <c r="AG36" t="n">
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
+      <c r="AI36" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3379,7 +3739,17 @@
           <t>110201</t>
         </is>
       </c>
-      <c r="AG37" t="n">
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
+      <c r="AI37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3458,7 +3828,17 @@
           <t>110201</t>
         </is>
       </c>
-      <c r="AG38" t="n">
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
+      <c r="AI38" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3535,7 +3915,17 @@
           <t>110501</t>
         </is>
       </c>
-      <c r="AG39" t="n">
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
+      <c r="AI39" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3612,7 +4002,17 @@
           <t>120305</t>
         </is>
       </c>
-      <c r="AG40" t="n">
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="AI40" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3689,7 +4089,17 @@
           <t>120601</t>
         </is>
       </c>
-      <c r="AG41" t="n">
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
+      <c r="AI41" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3768,7 +4178,17 @@
           <t>120606</t>
         </is>
       </c>
-      <c r="AG42" t="n">
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>UGEL PANGOA</t>
+        </is>
+      </c>
+      <c r="AI42" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3845,7 +4265,17 @@
           <t>120701</t>
         </is>
       </c>
-      <c r="AG43" t="n">
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
+      <c r="AI43" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3924,7 +4354,17 @@
           <t>120808</t>
         </is>
       </c>
-      <c r="AG44" t="n">
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>UGEL YAULI</t>
+        </is>
+      </c>
+      <c r="AI44" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4003,7 +4443,17 @@
           <t>130101</t>
         </is>
       </c>
-      <c r="AG45" t="n">
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
+      <c r="AI45" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4080,7 +4530,17 @@
           <t>090701</t>
         </is>
       </c>
-      <c r="AG46" t="n">
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
+      <c r="AI46" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4157,7 +4617,17 @@
           <t>130207</t>
         </is>
       </c>
-      <c r="AG47" t="n">
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="AI47" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4236,7 +4706,17 @@
           <t>130401</t>
         </is>
       </c>
-      <c r="AG48" t="n">
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
+      <c r="AI48" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4313,7 +4793,17 @@
           <t>130702</t>
         </is>
       </c>
-      <c r="AG49" t="n">
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
+      <c r="AI49" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4390,7 +4880,17 @@
           <t>130704</t>
         </is>
       </c>
-      <c r="AG50" t="n">
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
+      <c r="AI50" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4467,7 +4967,17 @@
           <t>140112</t>
         </is>
       </c>
-      <c r="AG51" t="n">
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
+      <c r="AI51" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4544,7 +5054,17 @@
           <t>140201</t>
         </is>
       </c>
-      <c r="AG52" t="n">
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
+      <c r="AI52" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4623,7 +5143,17 @@
           <t>140301</t>
         </is>
       </c>
-      <c r="AG53" t="n">
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AI53" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4700,7 +5230,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="AG54" t="n">
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="AI54" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4779,7 +5319,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="AG55" t="n">
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="AI55" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4856,7 +5406,17 @@
           <t>150113</t>
         </is>
       </c>
-      <c r="AG56" t="n">
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="AI56" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4933,7 +5493,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="AG57" t="n">
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="AI57" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5010,7 +5580,17 @@
           <t>150119</t>
         </is>
       </c>
-      <c r="AG58" t="n">
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI58" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5087,7 +5667,17 @@
           <t>150124</t>
         </is>
       </c>
-      <c r="AG59" t="n">
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI59" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5166,7 +5756,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="AG60" t="n">
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="AI60" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5243,7 +5843,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="AG61" t="n">
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="AI61" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5322,7 +5932,17 @@
           <t>150129</t>
         </is>
       </c>
-      <c r="AG62" t="n">
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI62" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5401,7 +6021,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="AG63" t="n">
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI63" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5480,7 +6110,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="AG64" t="n">
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI64" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5557,7 +6197,17 @@
           <t>150140</t>
         </is>
       </c>
-      <c r="AG65" t="n">
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="AI65" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5636,7 +6286,17 @@
           <t>150141</t>
         </is>
       </c>
-      <c r="AG66" t="n">
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="AI66" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5715,7 +6375,17 @@
           <t>150142</t>
         </is>
       </c>
-      <c r="AG67" t="n">
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI67" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5792,7 +6462,17 @@
           <t>150201</t>
         </is>
       </c>
-      <c r="AG68" t="n">
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
+      <c r="AI68" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5871,7 +6551,17 @@
           <t>150304</t>
         </is>
       </c>
-      <c r="AG69" t="n">
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
+      <c r="AI69" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5948,7 +6638,17 @@
           <t>150501</t>
         </is>
       </c>
-      <c r="AG70" t="n">
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
+      <c r="AI70" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6025,7 +6725,17 @@
           <t>150507</t>
         </is>
       </c>
-      <c r="AG71" t="n">
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
+      <c r="AI71" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6102,7 +6812,17 @@
           <t>150509</t>
         </is>
       </c>
-      <c r="AG72" t="n">
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
+      <c r="AI72" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6179,7 +6899,17 @@
           <t>150722</t>
         </is>
       </c>
-      <c r="AG73" t="n">
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
+      <c r="AI73" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6256,7 +6986,17 @@
           <t>150811</t>
         </is>
       </c>
-      <c r="AG74" t="n">
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
+      <c r="AI74" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6333,7 +7073,17 @@
           <t>150906</t>
         </is>
       </c>
-      <c r="AG75" t="n">
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>UGEL 14 OYÓN</t>
+        </is>
+      </c>
+      <c r="AI75" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6412,7 +7162,17 @@
           <t>160201</t>
         </is>
       </c>
-      <c r="AG76" t="n">
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
+      <c r="AI76" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6491,7 +7251,17 @@
           <t>120303</t>
         </is>
       </c>
-      <c r="AG77" t="n">
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
+      <c r="AI77" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6568,7 +7338,17 @@
           <t>190101</t>
         </is>
       </c>
-      <c r="AG78" t="n">
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
+      <c r="AI78" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6645,7 +7425,17 @@
           <t>190201</t>
         </is>
       </c>
-      <c r="AG79" t="n">
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>UGEL DANIEL ALCIDES CARRIÓN</t>
+        </is>
+      </c>
+      <c r="AI79" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6724,7 +7514,17 @@
           <t>190305</t>
         </is>
       </c>
-      <c r="AG80" t="n">
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>UGEL OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="AI80" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6801,7 +7601,17 @@
           <t>190306</t>
         </is>
       </c>
-      <c r="AG81" t="n">
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO BERMÚDEZ</t>
+        </is>
+      </c>
+      <c r="AI81" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6880,7 +7690,17 @@
           <t>200101</t>
         </is>
       </c>
-      <c r="AG82" t="n">
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
+      <c r="AI82" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6959,7 +7779,17 @@
           <t>200104</t>
         </is>
       </c>
-      <c r="AG83" t="n">
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
+      <c r="AI83" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7038,7 +7868,17 @@
           <t>200105</t>
         </is>
       </c>
-      <c r="AG84" t="n">
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
+      <c r="AI84" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7117,7 +7957,17 @@
           <t>200401</t>
         </is>
       </c>
-      <c r="AG85" t="n">
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
+      <c r="AI85" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7194,7 +8044,17 @@
           <t>200405</t>
         </is>
       </c>
-      <c r="AG86" t="n">
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
+      <c r="AI86" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7271,7 +8131,17 @@
           <t>200602</t>
         </is>
       </c>
-      <c r="AG87" t="n">
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
+      <c r="AI87" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7348,7 +8218,17 @@
           <t>200701</t>
         </is>
       </c>
-      <c r="AG88" t="n">
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
+      <c r="AI88" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7427,7 +8307,17 @@
           <t>200703</t>
         </is>
       </c>
-      <c r="AG89" t="n">
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
+      <c r="AI89" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7504,7 +8394,17 @@
           <t>210101</t>
         </is>
       </c>
-      <c r="AG90" t="n">
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
+      <c r="AI90" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7583,7 +8483,17 @@
           <t>210201</t>
         </is>
       </c>
-      <c r="AG91" t="n">
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
+      <c r="AI91" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7660,7 +8570,17 @@
           <t>210204</t>
         </is>
       </c>
-      <c r="AG92" t="n">
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
+      <c r="AI92" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7737,7 +8657,17 @@
           <t>210601</t>
         </is>
       </c>
-      <c r="AG93" t="n">
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
+      <c r="AI93" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7814,7 +8744,17 @@
           <t>210701</t>
         </is>
       </c>
-      <c r="AG94" t="n">
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
+      <c r="AI94" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7893,7 +8833,17 @@
           <t>210801</t>
         </is>
       </c>
-      <c r="AG95" t="n">
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
+      <c r="AI95" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7970,7 +8920,17 @@
           <t>211101</t>
         </is>
       </c>
-      <c r="AG96" t="n">
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
+      <c r="AI96" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8049,7 +9009,17 @@
           <t>220101</t>
         </is>
       </c>
-      <c r="AG97" t="n">
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="AI97" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8128,7 +9098,17 @@
           <t>220801</t>
         </is>
       </c>
-      <c r="AG98" t="n">
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
+      <c r="AI98" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8205,7 +9185,17 @@
           <t>220901</t>
         </is>
       </c>
-      <c r="AG99" t="n">
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
+      <c r="AI99" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8282,7 +9272,17 @@
           <t>220901</t>
         </is>
       </c>
-      <c r="AG100" t="n">
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
+      <c r="AI100" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8361,7 +9361,17 @@
           <t>221001</t>
         </is>
       </c>
-      <c r="AG101" t="n">
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
+      <c r="AI101" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8440,7 +9450,17 @@
           <t>130401</t>
         </is>
       </c>
-      <c r="AG102" t="n">
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
+      <c r="AI102" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8517,7 +9537,17 @@
           <t>240101</t>
         </is>
       </c>
-      <c r="AG103" t="n">
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
+      <c r="AI103" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8596,7 +9626,17 @@
           <t>240103</t>
         </is>
       </c>
-      <c r="AG104" t="n">
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
+      <c r="AI104" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8673,7 +9713,17 @@
           <t>200601</t>
         </is>
       </c>
-      <c r="AG105" t="n">
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
+      <c r="AI105" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8752,7 +9802,17 @@
           <t>150806</t>
         </is>
       </c>
-      <c r="AG106" t="n">
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
+      <c r="AI106" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8829,7 +9889,17 @@
           <t>120114</t>
         </is>
       </c>
-      <c r="AG107" t="n">
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
+      <c r="AI107" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8908,7 +9978,17 @@
           <t>070104</t>
         </is>
       </c>
-      <c r="AG108" t="n">
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AI108" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8985,7 +10065,17 @@
           <t>050101</t>
         </is>
       </c>
-      <c r="AG109" t="n">
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
+      <c r="AI109" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9062,7 +10152,17 @@
           <t>211105</t>
         </is>
       </c>
-      <c r="AG110" t="n">
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
+      <c r="AI110" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9139,7 +10239,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="AG111" t="n">
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="AI111" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9218,7 +10328,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="AG112" t="n">
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AI112" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9295,7 +10415,17 @@
           <t>030602</t>
         </is>
       </c>
-      <c r="AG113" t="n">
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AI113" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9374,7 +10504,17 @@
           <t>090608</t>
         </is>
       </c>
-      <c r="AG114" t="n">
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
+      <c r="AI114" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9451,7 +10591,17 @@
           <t>040128</t>
         </is>
       </c>
-      <c r="AG115" t="n">
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI115" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9530,7 +10680,17 @@
           <t>150305</t>
         </is>
       </c>
-      <c r="AG116" t="n">
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
+      <c r="AI116" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9607,7 +10767,17 @@
           <t>030101</t>
         </is>
       </c>
-      <c r="AG117" t="n">
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
+      <c r="AI117" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9684,7 +10854,17 @@
           <t>190103</t>
         </is>
       </c>
-      <c r="AG118" t="n">
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
+      <c r="AI118" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9763,7 +10943,17 @@
           <t>130205</t>
         </is>
       </c>
-      <c r="AG119" t="n">
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="AI119" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9842,7 +11032,17 @@
           <t>130206</t>
         </is>
       </c>
-      <c r="AG120" t="n">
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="AI120" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9919,7 +11119,17 @@
           <t>050801</t>
         </is>
       </c>
-      <c r="AG121" t="n">
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>UGEL PAUCAR DE SARASARA</t>
+        </is>
+      </c>
+      <c r="AI121" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9996,7 +11206,17 @@
           <t>200602</t>
         </is>
       </c>
-      <c r="AG122" t="n">
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
+      <c r="AI122" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10075,7 +11295,17 @@
           <t>070106</t>
         </is>
       </c>
-      <c r="AG123" t="n">
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="AI123" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10152,7 +11382,17 @@
           <t>250201</t>
         </is>
       </c>
-      <c r="AG124" t="n">
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>UGEL ATALAYA</t>
+        </is>
+      </c>
+      <c r="AI124" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10229,7 +11469,17 @@
           <t>061001</t>
         </is>
       </c>
-      <c r="AG125" t="n">
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="AI125" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10306,7 +11556,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="AG126" t="n">
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="AI126" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10385,7 +11645,17 @@
           <t>070106</t>
         </is>
       </c>
-      <c r="AG127" t="n">
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="AI127" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10462,7 +11732,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="AG128" t="n">
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="AI128" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10541,7 +11821,17 @@
           <t>090118</t>
         </is>
       </c>
-      <c r="AG129" t="n">
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AI129" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10620,7 +11910,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="AG130" t="n">
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AI130" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10697,7 +11997,17 @@
           <t>210203</t>
         </is>
       </c>
-      <c r="AG131" t="n">
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
+      <c r="AI131" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10774,7 +12084,17 @@
           <t>030601</t>
         </is>
       </c>
-      <c r="AG132" t="n">
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AI132" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10851,7 +12171,17 @@
           <t>110507</t>
         </is>
       </c>
-      <c r="AG133" t="n">
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
+      <c r="AI133" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10928,7 +12258,17 @@
           <t>130701</t>
         </is>
       </c>
-      <c r="AG134" t="n">
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
+      <c r="AI134" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11007,7 +12347,17 @@
           <t>130202</t>
         </is>
       </c>
-      <c r="AG135" t="n">
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="AI135" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11086,7 +12436,17 @@
           <t>040520</t>
         </is>
       </c>
-      <c r="AG136" t="n">
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AI136" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11163,7 +12523,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="AG137" t="n">
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="AI137" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11242,7 +12612,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="AG138" t="n">
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="AI138" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11321,7 +12701,17 @@
           <t>150118</t>
         </is>
       </c>
-      <c r="AG139" t="n">
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="AI139" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11398,7 +12788,17 @@
           <t>200504</t>
         </is>
       </c>
-      <c r="AG140" t="n">
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
+      <c r="AI140" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11477,7 +12877,17 @@
           <t>150801</t>
         </is>
       </c>
-      <c r="AG141" t="n">
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
+      <c r="AI141" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11556,7 +12966,17 @@
           <t>151001</t>
         </is>
       </c>
-      <c r="AG142" t="n">
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
+      <c r="AI142" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11633,7 +13053,17 @@
           <t>200114</t>
         </is>
       </c>
-      <c r="AG143" t="n">
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
+      <c r="AI143" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11712,7 +13142,17 @@
           <t>080301</t>
         </is>
       </c>
-      <c r="AG144" t="n">
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
+      <c r="AI144" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11789,7 +13229,17 @@
           <t>150142</t>
         </is>
       </c>
-      <c r="AG145" t="n">
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AI145" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11868,7 +13318,17 @@
           <t>100102</t>
         </is>
       </c>
-      <c r="AG146" t="n">
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
+      <c r="AI146" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11947,7 +13407,17 @@
           <t>160113</t>
         </is>
       </c>
-      <c r="AG147" t="n">
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
+      <c r="AI147" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12024,7 +13494,17 @@
           <t>050702</t>
         </is>
       </c>
-      <c r="AG148" t="n">
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
+      <c r="AI148" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12103,7 +13583,17 @@
           <t>120502</t>
         </is>
       </c>
-      <c r="AG149" t="n">
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>UGEL JUNÍN</t>
+        </is>
+      </c>
+      <c r="AI149" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12182,7 +13672,17 @@
           <t>220201</t>
         </is>
       </c>
-      <c r="AG150" t="n">
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="AI150" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12261,7 +13761,17 @@
           <t>221005</t>
         </is>
       </c>
-      <c r="AG151" t="n">
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
+      <c r="AI151" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12338,7 +13848,17 @@
           <t>010205</t>
         </is>
       </c>
-      <c r="AG152" t="n">
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
+      <c r="AI152" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12417,7 +13937,17 @@
           <t>131201</t>
         </is>
       </c>
-      <c r="AG153" t="n">
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
+      <c r="AI153" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12496,7 +14026,17 @@
           <t>131202</t>
         </is>
       </c>
-      <c r="AG154" t="n">
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
+      <c r="AI154" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12573,7 +14113,17 @@
           <t>240105</t>
         </is>
       </c>
-      <c r="AG155" t="n">
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
+      <c r="AI155" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12652,7 +14202,17 @@
           <t>240201</t>
         </is>
       </c>
-      <c r="AG156" t="n">
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
+      <c r="AI156" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12729,7 +14289,17 @@
           <t>240301</t>
         </is>
       </c>
-      <c r="AG157" t="n">
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
+      <c r="AI157" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12808,7 +14378,17 @@
           <t>110304</t>
         </is>
       </c>
-      <c r="AG158" t="n">
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
+      <c r="AI158" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12885,7 +14465,17 @@
           <t>030604</t>
         </is>
       </c>
-      <c r="AG159" t="n">
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AI159" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12964,7 +14554,17 @@
           <t>021809</t>
         </is>
       </c>
-      <c r="AG160" t="n">
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
+      <c r="AI160" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13043,7 +14643,17 @@
           <t>040121</t>
         </is>
       </c>
-      <c r="AG161" t="n">
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AI161" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13120,7 +14730,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="AG162" t="n">
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="AI162" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13199,7 +14819,17 @@
           <t>061303</t>
         </is>
       </c>
-      <c r="AG163" t="n">
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="AI163" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13278,7 +14908,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="AG164" t="n">
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AI164" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13355,7 +14995,17 @@
           <t>081005</t>
         </is>
       </c>
-      <c r="AG165" t="n">
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>UGEL PARURO</t>
+        </is>
+      </c>
+      <c r="AI165" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13434,7 +15084,17 @@
           <t>240304</t>
         </is>
       </c>
-      <c r="AG166" t="n">
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
+      <c r="AI166" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13511,7 +15171,17 @@
           <t>080302</t>
         </is>
       </c>
-      <c r="AG167" t="n">
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
+      <c r="AI167" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13590,7 +15260,17 @@
           <t>130208</t>
         </is>
       </c>
-      <c r="AG168" t="n">
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
+      <c r="AI168" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13667,7 +15347,17 @@
           <t>210101</t>
         </is>
       </c>
-      <c r="AG169" t="n">
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
+      <c r="AI169" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13744,7 +15434,17 @@
           <t>220910</t>
         </is>
       </c>
-      <c r="AG170" t="n">
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
+      <c r="AI170" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13823,7 +15523,17 @@
           <t>110207</t>
         </is>
       </c>
-      <c r="AG171" t="n">
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
+      <c r="AI171" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13900,7 +15610,17 @@
           <t>190306</t>
         </is>
       </c>
-      <c r="AG172" t="n">
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO BERMÚDEZ</t>
+        </is>
+      </c>
+      <c r="AI172" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13977,7 +15697,17 @@
           <t>250304</t>
         </is>
       </c>
-      <c r="AG173" t="n">
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
+      <c r="AI173" t="n">
         <v>2026</v>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI173"/>
+  <dimension ref="A1:AJ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,11 @@
       <c r="AI1" t="inlineStr">
         <is>
           <t>anio</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -681,6 +686,11 @@
       <c r="AI2" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -768,6 +778,11 @@
       <c r="AI3" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -857,6 +872,11 @@
       <c r="AI4" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -946,6 +966,11 @@
       <c r="AI5" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1033,6 +1058,11 @@
       <c r="AI6" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1120,6 +1150,11 @@
       <c r="AI7" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1207,6 +1242,11 @@
       <c r="AI8" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1294,6 +1334,11 @@
       <c r="AI9" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1383,6 +1428,11 @@
       <c r="AI10" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1472,6 +1522,11 @@
       <c r="AI11" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1559,6 +1614,11 @@
       <c r="AI12" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1646,6 +1706,11 @@
       <c r="AI13" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1733,6 +1798,11 @@
       <c r="AI14" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1820,6 +1890,11 @@
       <c r="AI15" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1907,6 +1982,11 @@
       <c r="AI16" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1994,6 +2074,11 @@
       <c r="AI17" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2081,6 +2166,11 @@
       <c r="AI18" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2170,6 +2260,11 @@
       <c r="AI19" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2257,6 +2352,11 @@
       <c r="AI20" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2346,6 +2446,11 @@
       <c r="AI21" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2433,6 +2538,11 @@
       <c r="AI22" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2520,6 +2630,11 @@
       <c r="AI23" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2607,6 +2722,11 @@
       <c r="AI24" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2696,6 +2816,11 @@
       <c r="AI25" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2783,6 +2908,11 @@
       <c r="AI26" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2872,6 +3002,11 @@
       <c r="AI27" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2959,6 +3094,11 @@
       <c r="AI28" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3046,6 +3186,11 @@
       <c r="AI29" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3135,6 +3280,11 @@
       <c r="AI30" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3224,6 +3374,11 @@
       <c r="AI31" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3311,6 +3466,11 @@
       <c r="AI32" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3398,6 +3558,11 @@
       <c r="AI33" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3487,6 +3652,11 @@
       <c r="AI34" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3576,6 +3746,11 @@
       <c r="AI35" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3665,6 +3840,11 @@
       <c r="AI36" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3752,6 +3932,11 @@
       <c r="AI37" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3841,6 +4026,11 @@
       <c r="AI38" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3928,6 +4118,11 @@
       <c r="AI39" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4015,6 +4210,11 @@
       <c r="AI40" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4102,6 +4302,11 @@
       <c r="AI41" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4191,6 +4396,11 @@
       <c r="AI42" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4278,6 +4488,11 @@
       <c r="AI43" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4367,6 +4582,11 @@
       <c r="AI44" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4456,6 +4676,11 @@
       <c r="AI45" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4543,6 +4768,11 @@
       <c r="AI46" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4630,6 +4860,11 @@
       <c r="AI47" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4719,6 +4954,11 @@
       <c r="AI48" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4806,6 +5046,11 @@
       <c r="AI49" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4893,6 +5138,11 @@
       <c r="AI50" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4980,6 +5230,11 @@
       <c r="AI51" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5067,6 +5322,11 @@
       <c r="AI52" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5156,6 +5416,11 @@
       <c r="AI53" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5243,6 +5508,11 @@
       <c r="AI54" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5332,6 +5602,11 @@
       <c r="AI55" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5419,6 +5694,11 @@
       <c r="AI56" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5506,6 +5786,11 @@
       <c r="AI57" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5593,6 +5878,11 @@
       <c r="AI58" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5680,6 +5970,11 @@
       <c r="AI59" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5769,6 +6064,11 @@
       <c r="AI60" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5856,6 +6156,11 @@
       <c r="AI61" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5945,6 +6250,11 @@
       <c r="AI62" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6034,6 +6344,11 @@
       <c r="AI63" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6123,6 +6438,11 @@
       <c r="AI64" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6210,6 +6530,11 @@
       <c r="AI65" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6299,6 +6624,11 @@
       <c r="AI66" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6388,6 +6718,11 @@
       <c r="AI67" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6475,6 +6810,11 @@
       <c r="AI68" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6564,6 +6904,11 @@
       <c r="AI69" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6651,6 +6996,11 @@
       <c r="AI70" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6738,6 +7088,11 @@
       <c r="AI71" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6825,6 +7180,11 @@
       <c r="AI72" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6912,6 +7272,11 @@
       <c r="AI73" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6999,6 +7364,11 @@
       <c r="AI74" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7086,6 +7456,11 @@
       <c r="AI75" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7175,6 +7550,11 @@
       <c r="AI76" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7264,6 +7644,11 @@
       <c r="AI77" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7351,6 +7736,11 @@
       <c r="AI78" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7438,6 +7828,11 @@
       <c r="AI79" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7527,6 +7922,11 @@
       <c r="AI80" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7614,6 +8014,11 @@
       <c r="AI81" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7703,6 +8108,11 @@
       <c r="AI82" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7792,6 +8202,11 @@
       <c r="AI83" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7881,6 +8296,11 @@
       <c r="AI84" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7970,6 +8390,11 @@
       <c r="AI85" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8057,6 +8482,11 @@
       <c r="AI86" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8144,6 +8574,11 @@
       <c r="AI87" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8231,6 +8666,11 @@
       <c r="AI88" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8320,6 +8760,11 @@
       <c r="AI89" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8407,6 +8852,11 @@
       <c r="AI90" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8496,6 +8946,11 @@
       <c r="AI91" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8583,6 +9038,11 @@
       <c r="AI92" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8670,6 +9130,11 @@
       <c r="AI93" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8757,6 +9222,11 @@
       <c r="AI94" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8846,6 +9316,11 @@
       <c r="AI95" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8933,6 +9408,11 @@
       <c r="AI96" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9022,6 +9502,11 @@
       <c r="AI97" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9111,6 +9596,11 @@
       <c r="AI98" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9198,6 +9688,11 @@
       <c r="AI99" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9285,6 +9780,11 @@
       <c r="AI100" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9374,6 +9874,11 @@
       <c r="AI101" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9463,6 +9968,11 @@
       <c r="AI102" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9550,6 +10060,11 @@
       <c r="AI103" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9639,6 +10154,11 @@
       <c r="AI104" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9726,6 +10246,11 @@
       <c r="AI105" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9815,6 +10340,11 @@
       <c r="AI106" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9902,6 +10432,11 @@
       <c r="AI107" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9991,6 +10526,11 @@
       <c r="AI108" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10078,6 +10618,11 @@
       <c r="AI109" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10165,6 +10710,11 @@
       <c r="AI110" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10252,6 +10802,11 @@
       <c r="AI111" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10341,6 +10896,11 @@
       <c r="AI112" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10428,6 +10988,11 @@
       <c r="AI113" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10517,6 +11082,11 @@
       <c r="AI114" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10604,6 +11174,11 @@
       <c r="AI115" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10693,6 +11268,11 @@
       <c r="AI116" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10780,6 +11360,11 @@
       <c r="AI117" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10867,6 +11452,11 @@
       <c r="AI118" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10956,6 +11546,11 @@
       <c r="AI119" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11045,6 +11640,11 @@
       <c r="AI120" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11132,6 +11732,11 @@
       <c r="AI121" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11219,6 +11824,11 @@
       <c r="AI122" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11308,6 +11918,11 @@
       <c r="AI123" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11395,6 +12010,11 @@
       <c r="AI124" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11482,6 +12102,11 @@
       <c r="AI125" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11569,6 +12194,11 @@
       <c r="AI126" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11658,6 +12288,11 @@
       <c r="AI127" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11745,6 +12380,11 @@
       <c r="AI128" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11834,6 +12474,11 @@
       <c r="AI129" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11923,6 +12568,11 @@
       <c r="AI130" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -12010,6 +12660,11 @@
       <c r="AI131" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -12097,6 +12752,11 @@
       <c r="AI132" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -12184,6 +12844,11 @@
       <c r="AI133" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -12271,6 +12936,11 @@
       <c r="AI134" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -12360,6 +13030,11 @@
       <c r="AI135" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -12449,6 +13124,11 @@
       <c r="AI136" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12536,6 +13216,11 @@
       <c r="AI137" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -12625,6 +13310,11 @@
       <c r="AI138" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -12714,6 +13404,11 @@
       <c r="AI139" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -12801,6 +13496,11 @@
       <c r="AI140" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12890,6 +13590,11 @@
       <c r="AI141" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -12979,6 +13684,11 @@
       <c r="AI142" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -13066,6 +13776,11 @@
       <c r="AI143" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13155,6 +13870,11 @@
       <c r="AI144" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -13242,6 +13962,11 @@
       <c r="AI145" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -13331,6 +14056,11 @@
       <c r="AI146" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -13420,6 +14150,11 @@
       <c r="AI147" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -13507,6 +14242,11 @@
       <c r="AI148" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -13596,6 +14336,11 @@
       <c r="AI149" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -13685,6 +14430,11 @@
       <c r="AI150" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13774,6 +14524,11 @@
       <c r="AI151" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -13861,6 +14616,11 @@
       <c r="AI152" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -13950,6 +14710,11 @@
       <c r="AI153" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -14039,6 +14804,11 @@
       <c r="AI154" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -14126,6 +14896,11 @@
       <c r="AI155" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -14215,6 +14990,11 @@
       <c r="AI156" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -14302,6 +15082,11 @@
       <c r="AI157" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -14391,6 +15176,11 @@
       <c r="AI158" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14478,6 +15268,11 @@
       <c r="AI159" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14567,6 +15362,11 @@
       <c r="AI160" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14656,6 +15456,11 @@
       <c r="AI161" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14743,6 +15548,11 @@
       <c r="AI162" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14832,6 +15642,11 @@
       <c r="AI163" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -14921,6 +15736,11 @@
       <c r="AI164" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -15008,6 +15828,11 @@
       <c r="AI165" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -15097,6 +15922,11 @@
       <c r="AI166" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -15184,6 +16014,11 @@
       <c r="AI167" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -15273,6 +16108,11 @@
       <c r="AI168" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -15360,6 +16200,11 @@
       <c r="AI169" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -15447,6 +16292,11 @@
       <c r="AI170" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -15536,6 +16386,11 @@
       <c r="AI171" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -15623,6 +16478,11 @@
       <c r="AI172" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -15710,6 +16570,11 @@
       <c r="AI173" t="n">
         <v>2026</v>
       </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ173"/>
+  <dimension ref="A1:AL173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,10 +589,20 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -683,10 +693,20 @@
           <t>UGEL BAGUA</t>
         </is>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>001/001</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -775,10 +795,20 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -869,10 +899,20 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
-      <c r="AI4" t="n">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>02 AGUSTIN EVANS/02 AGUSTIN EVANS</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -963,10 +1003,20 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>FE Y ALEGRIA 42/FE Y ALEGRIA 42</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1055,10 +1105,20 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
-      <c r="AI6" t="n">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>03 NUEVO CHIMBOTE/03 NUEVO CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1147,10 +1207,20 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
-      <c r="AI7" t="n">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>01 PIERRE FRANCOIS JAMET/01 PIERRE FRANCOIS JAMET</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1239,10 +1309,20 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
-      <c r="AI8" t="n">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>07/PRITE 02 CURAHUASI/07</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1331,10 +1411,20 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>PRITE ANDAHUAYLAS/ANDAHUAYLAS/ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1425,10 +1515,20 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1519,10 +1619,20 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
-      <c r="AI11" t="n">
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1611,10 +1721,20 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
-      <c r="AI12" t="n">
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>NUESTRA SEÑORA DEL PILAR/NUESTRA SEÑORA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1703,10 +1823,20 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>AUVERGNE PERU - FRANCIA/AUVERGNE PERU - FRANCIA</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1795,10 +1925,20 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>NUESTRA SRA. DE LA CANDELARIA/NUESTRA SRA. DE LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1887,10 +2027,20 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>MARIA DE LA ESPERANZA/MARIA DE LA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -1979,10 +2129,20 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES/SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2071,10 +2231,20 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>NUESTRA SRA. DEL PERPETUO SOCORRO/NUESTRA SRA. DEL PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2163,10 +2333,20 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
-      <c r="AI18" t="n">
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>HELEN KELLER/HELEN KELLER</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2257,10 +2437,20 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>MEDALLA MILAGROSA/MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2349,10 +2539,20 @@
           <t>UGEL ISLAY</t>
         </is>
       </c>
-      <c r="AI20" t="n">
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>MOLLENDO/MOLLENDO</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2443,10 +2643,20 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
-      <c r="AI21" t="n">
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>LURICOCHA</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2535,10 +2745,20 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
-      <c r="AI22" t="n">
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>IMMANUEL KANT PUQUIO</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2627,10 +2847,20 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
-      <c r="AI23" t="n">
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>020 CLEMENTINA BRAVO DE NOBLECILLA/020 CLEMENTINA BRAVO DE NOBLECILLA</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2719,10 +2949,20 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
-      <c r="AI24" t="n">
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>PRITE SEÑOR DE LA DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2813,10 +3053,20 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
-      <c r="AI25" t="n">
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>CHOTA/CHOTA</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2905,10 +3155,20 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
-      <c r="AI26" t="n">
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -2999,10 +3259,20 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
-      <c r="AI27" t="n">
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>SAN ANTONIO/SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3091,10 +3361,20 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
-      <c r="AI28" t="n">
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3183,10 +3463,20 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>LA PERLA/LA PERLA</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AL29" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3277,10 +3567,20 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
-      <c r="AI30" t="n">
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO DE ASIS/SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ30" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3371,10 +3671,20 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
-      <c r="AI31" t="n">
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>NUESTRA SEÑORA DEL CARMEN/NUESTRA SEÑORA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3463,10 +3773,20 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
-      <c r="AI32" t="n">
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>PRITE SEÑOR DE LA VARA/SEÑOR DE LA VARA/SEÑOR DE LA VARA</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3555,10 +3875,20 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
-      <c r="AI33" t="n">
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL/PRITE SAN MIGUEL/SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ33" t="inlineStr">
+      <c r="AL33" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3649,10 +3979,20 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
-      <c r="AI34" t="n">
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>PRITE SAGRADA FAMILIA/SAGRADA FAMILIA/SAGRADA FAMILIA</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3743,10 +4083,20 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
-      <c r="AI35" t="n">
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>35001/35001</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK35" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3837,10 +4187,20 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
-      <c r="AI36" t="n">
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>PRITE CAMANA</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK36" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ36" t="inlineStr">
+      <c r="AL36" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -3929,10 +4289,20 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
-      <c r="AI37" t="n">
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>CHINCHA/CHINCHA</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4023,10 +4393,20 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
-      <c r="AI38" t="n">
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>SANTA CECILIA/SANTA CECILIA</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ38" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4115,10 +4495,20 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
-      <c r="AI39" t="n">
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>PISCO/PISCO</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ39" t="inlineStr">
+      <c r="AL39" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4207,10 +4597,20 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
-      <c r="AI40" t="n">
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>SAN MANUELITO/SAN MANUELITO</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ40" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4299,10 +4699,20 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
-      <c r="AI41" t="n">
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>NIÑO JESUCITO/NIÑO JESUCITO</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AL41" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4393,10 +4803,20 @@
           <t>UGEL PANGOA</t>
         </is>
       </c>
-      <c r="AI42" t="n">
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ42" t="inlineStr">
+      <c r="AL42" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4485,10 +4905,20 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
-      <c r="AI43" t="n">
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>SEÑOR DE MURUHUAY/PRITE GOTITAS DE AMOR/SEÑOR DE MURUHUAY</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ43" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4579,10 +5009,20 @@
           <t>UGEL YAULI</t>
         </is>
       </c>
-      <c r="AI44" t="n">
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>DOMINGO SAVIO/PRITE JUAN PABLO II/DOMINGO SAVIO</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ44" t="inlineStr">
+      <c r="AL44" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4673,10 +5113,20 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
-      <c r="AI45" t="n">
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>TULIO HERRERA LEON/TULIO HERRERA LEON</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ45" t="inlineStr">
+      <c r="AL45" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4765,10 +5215,20 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
-      <c r="AI46" t="n">
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>35002/35002</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ46" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4857,10 +5317,20 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
-      <c r="AI47" t="n">
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>CARTAVIO/CARTAVIO</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ47" t="inlineStr">
+      <c r="AL47" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -4951,10 +5421,20 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
-      <c r="AI48" t="n">
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>CHEPEN/CHEPEN</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ48" t="inlineStr">
+      <c r="AL48" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5043,10 +5523,20 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
-      <c r="AI49" t="n">
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>DEJAD QUE LOS NIÑOS VENGAN A MI/DEJAD QUE LOS NIÑOS VENGAN A MI</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ49" t="inlineStr">
+      <c r="AL49" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5135,10 +5625,20 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
-      <c r="AI50" t="n">
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>PACASMAYO/PACASMAYO</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ50" t="inlineStr">
+      <c r="AL50" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5227,10 +5727,20 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
-      <c r="AI51" t="n">
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>NIÑO JESUS DE PRAGA/NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AL51" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5319,10 +5829,20 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
-      <c r="AI52" t="n">
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>SAN JUDAS TADEO/SAN JUDAS TADEO</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5413,10 +5933,20 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
-      <c r="AI53" t="n">
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>SAN PEDRO/PRITE SAN PEDRO/SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5505,10 +6035,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="AI54" t="n">
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>06 REPUBLICA DOMINICANA/06 REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5599,10 +6139,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="AI55" t="n">
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>15 MADRE TERESA DE CALCUTA/15 MADRE TERESA DE CALCUTA</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5691,10 +6241,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="AI56" t="n">
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>08 PERU HOLANDA/08 PERU HOLANDA</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5783,10 +6343,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="AI57" t="n">
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>MANUEL DUATO/MANUEL DUATO</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5875,10 +6445,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI58" t="n">
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>LURIN/LURIN</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -5967,10 +6547,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI59" t="n">
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>10 SAGRADO CORAZON DE JESUS/10 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6061,10 +6651,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="AI60" t="n">
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>JERUSALEN</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6153,10 +6753,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="AI61" t="n">
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>RICARDO BENTIN/RICARDO BENTIN</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6247,10 +6857,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI62" t="n">
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6341,10 +6961,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI63" t="n">
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>RVDA. MADRE MARIANA CARRIGAN/RVDA. MADRE MARIANA CARRIGAN</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6435,10 +7065,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI64" t="n">
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>NUESTRA SEÑORA DE GUADALUPE/NUESTRA SEÑORA DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6527,10 +7167,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="AI65" t="n">
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>09 SAN FRANCISCO DE ASIS/09 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6621,10 +7271,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="AI66" t="n">
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>ESPECIAL SURQUILLO/PRITE ALEGRIA EN EL CORAZON/ESPECIAL SURQUILLO</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AL66" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6715,10 +7375,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI67" t="n">
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>DIVINA MISERICORDIA/DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6807,10 +7477,20 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
-      <c r="AI68" t="n">
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>FERNANDO CARBAJAL SEGURA/FERNANDO CARBAJAL SEGURA</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6901,10 +7581,20 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
-      <c r="AI69" t="n">
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>CAJAMARQUILLA</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -6993,10 +7683,20 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
-      <c r="AI70" t="n">
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>05 SAN MARCELINO CHAMPAGNAT/05 SAN MARCELINO CHAMPAGNAT</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7085,10 +7785,20 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
-      <c r="AI71" t="n">
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>04/04</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7177,10 +7887,20 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
-      <c r="AI72" t="n">
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>003 DIVINO JESUS/003 DIVINO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7269,10 +7989,20 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
-      <c r="AI73" t="n">
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>SAN MATEO DE HUANCHOR/SAN MATEO DE HUANCHOR</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7361,10 +8091,20 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
-      <c r="AI74" t="n">
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>03 DIVINO NIÑO JESUS/03 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AL74" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7453,10 +8193,20 @@
           <t>UGEL 14 OYÓN</t>
         </is>
       </c>
-      <c r="AI75" t="n">
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>CHURIN/CHURIN</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AL75" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7547,10 +8297,20 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
-      <c r="AI76" t="n">
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>PRITE YURIMAGUAS/BONIFACIO ALVARADO PAREDES/BONIFACIO ALVARADO PAREDES</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK76" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="AL76" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7641,10 +8401,20 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
-      <c r="AI77" t="n">
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>LOS NIÑOS DE JESUS/LOS NIÑOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK77" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AL77" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7733,10 +8503,20 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
-      <c r="AI78" t="n">
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRAS/SAN MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK78" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AL78" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7825,10 +8605,20 @@
           <t>UGEL DANIEL ALCIDES CARRIÓN</t>
         </is>
       </c>
-      <c r="AI79" t="n">
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>ESPECIAL YANAHUANCA/PRITE YANAHUANCA/ESPECIAL YANAHUANCA</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK79" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ79" t="inlineStr">
+      <c r="AL79" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -7919,10 +8709,20 @@
           <t>UGEL OXAPAMPA</t>
         </is>
       </c>
-      <c r="AI80" t="n">
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>MAESTRA CAROLINA EGG JOHANN/MAESTRA CAROLINA EGG JOHANN</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK80" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ80" t="inlineStr">
+      <c r="AL80" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8011,10 +8811,20 @@
           <t>UGEL PUERTO BERMÚDEZ</t>
         </is>
       </c>
-      <c r="AI81" t="n">
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>LA INMACULADA/LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK81" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AL81" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8105,10 +8915,20 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
-      <c r="AI82" t="n">
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>PAUL HARRIS/PAUL HARRIS</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK82" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AL82" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8199,10 +9019,20 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
-      <c r="AI83" t="n">
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>CASTILLA/CASTILLA</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK83" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ83" t="inlineStr">
+      <c r="AL83" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8293,10 +9123,20 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
-      <c r="AI84" t="n">
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>HEROICA VILLA/HEROICA VILLA</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK84" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ84" t="inlineStr">
+      <c r="AL84" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8387,10 +9227,20 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
-      <c r="AI85" t="n">
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>JESUS DE NAZARENO</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK85" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ85" t="inlineStr">
+      <c r="AL85" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8479,10 +9329,20 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
-      <c r="AI86" t="n">
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>FRAY MARTIN DE PORRAS/FRAY MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK86" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ86" t="inlineStr">
+      <c r="AL86" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8571,10 +9431,20 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
-      <c r="AI87" t="n">
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>HIJOS DE MARIA/HIJOS DE MARIA</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK87" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ87" t="inlineStr">
+      <c r="AL87" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8663,10 +9533,20 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
-      <c r="AI88" t="n">
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>PRITE NUESTRA SEÑORA DEL PERPETUO SOCORRO/NUESTRA SEÑORA DEL PERPETUO SOCORRO/NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK88" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AL88" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8757,10 +9637,20 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
-      <c r="AI89" t="n">
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>NEGRITOS/NEGRITOS</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK89" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ89" t="inlineStr">
+      <c r="AL89" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8849,10 +9739,20 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
-      <c r="AI90" t="n">
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>NUESTRA SEÑORA DE COPACABANA/NUESTRA SEÑORA DE COPACABANA</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK90" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AL90" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -8943,10 +9843,20 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
-      <c r="AI91" t="n">
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>MADRE FRANCISCA PASCUAL DOMENECH/MADRE FRANCISCA PASCUAL DOMENECH</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK91" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AL91" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9035,10 +9945,20 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
-      <c r="AI92" t="n">
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>ASILLO/ASILLO</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK92" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ92" t="inlineStr">
+      <c r="AL92" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9127,10 +10047,20 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
-      <c r="AI93" t="n">
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>VIRGEN DE FATIMA/VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK93" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ93" t="inlineStr">
+      <c r="AL93" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9219,10 +10149,20 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
-      <c r="AI94" t="n">
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>JUAN GNALDI COLESCHI/JUAN GNALDI COLESCHI</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK94" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ94" t="inlineStr">
+      <c r="AL94" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9313,10 +10253,20 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
-      <c r="AI95" t="n">
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK95" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ95" t="inlineStr">
+      <c r="AL95" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9405,10 +10355,20 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
-      <c r="AI96" t="n">
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK96" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ96" t="inlineStr">
+      <c r="AL96" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9499,10 +10459,20 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
-      <c r="AI97" t="n">
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>00002/00002</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK97" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AL97" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9593,10 +10563,20 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
-      <c r="AI98" t="n">
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>00003/00003</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK98" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AL98" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9685,10 +10665,20 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
-      <c r="AI99" t="n">
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>0001 VIRGEN DEL CARMEN/0001 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK99" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AL99" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9777,10 +10767,20 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
-      <c r="AI100" t="n">
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>0002 REHABILITACION Y EDUCACION DEL CIEGO/0002 REHABILITACION Y EDUCACION DEL CIEGO</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK100" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AL100" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9871,10 +10871,20 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
-      <c r="AI101" t="n">
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>FREDY ALIAGA CARDENAS/FREDY ALIAGA CARDENAS</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK101" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ101" t="inlineStr">
+      <c r="AL101" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -9965,10 +10975,20 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
-      <c r="AI102" t="n">
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>PRITE CHEPEN</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK102" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ102" t="inlineStr">
+      <c r="AL102" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10057,10 +11077,20 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
-      <c r="AI103" t="n">
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>001 SAN JUAN DE DIOS/001 SAN JUAN DE DIOS</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK103" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ103" t="inlineStr">
+      <c r="AL103" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10151,10 +11181,20 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
-      <c r="AI104" t="n">
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>006 NIÑO JESUS DE PRAGA/006 NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK104" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ104" t="inlineStr">
+      <c r="AL104" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10243,10 +11283,20 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
-      <c r="AI105" t="n">
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>PRITE VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK105" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ105" t="inlineStr">
+      <c r="AL105" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10337,10 +11387,20 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
-      <c r="AI106" t="n">
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>02 SAN FRANCISCO DE ASIS/02 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK106" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ106" t="inlineStr">
+      <c r="AL106" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10429,10 +11489,20 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
-      <c r="AI107" t="n">
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>POLIVALENTE/POLIVALENTE</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK107" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ107" t="inlineStr">
+      <c r="AL107" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10523,10 +11593,20 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
-      <c r="AI108" t="n">
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>LUISA SOLOGUREN DE SABOGAL/LUISA SOLOGUREN DE SABOGAL</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK108" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ108" t="inlineStr">
+      <c r="AL108" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10615,10 +11695,20 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
-      <c r="AI109" t="n">
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>PRITE I</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK109" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ109" t="inlineStr">
+      <c r="AL109" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10707,10 +11797,20 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
-      <c r="AI110" t="n">
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>PRITE DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK110" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ110" t="inlineStr">
+      <c r="AL110" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10799,10 +11899,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="AI111" t="n">
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>PRITE ANTARES</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK111" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ111" t="inlineStr">
+      <c r="AL111" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10893,10 +12003,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="AI112" t="n">
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>PRITE AYUDAME</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK112" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ112" t="inlineStr">
+      <c r="AL112" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -10985,10 +12105,20 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
-      <c r="AI113" t="n">
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>URIPA/URIPA</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK113" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ113" t="inlineStr">
+      <c r="AL113" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11079,10 +12209,20 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
-      <c r="AI114" t="n">
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>35011/35011</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK114" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ114" t="inlineStr">
+      <c r="AL114" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11171,10 +12311,20 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
-      <c r="AI115" t="n">
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>PRITE YURA</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK115" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ115" t="inlineStr">
+      <c r="AL115" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11265,10 +12415,20 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
-      <c r="AI116" t="n">
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>CAHUA/CAHUA</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK116" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ116" t="inlineStr">
+      <c r="AL116" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11357,10 +12517,20 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
-      <c r="AI117" t="n">
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>11 SANT GERMA JAUME HILARI BARBAL LA SALLE/11 SANT GERMA JAUME HILARI BARBAL LA SALLE</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK117" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AL117" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11449,10 +12619,20 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
-      <c r="AI118" t="n">
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK118" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ118" t="inlineStr">
+      <c r="AL118" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11543,10 +12723,20 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
-      <c r="AI119" t="n">
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>PAIJAN/PAIJAN</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK119" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ119" t="inlineStr">
+      <c r="AL119" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11637,10 +12827,20 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
-      <c r="AI120" t="n">
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>DIVINO NIÑO DEL MILAGRO/DIVINO NIÑO DEL MILAGRO</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK120" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ120" t="inlineStr">
+      <c r="AL120" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11729,10 +12929,20 @@
           <t>UGEL PAUCAR DE SARASARA</t>
         </is>
       </c>
-      <c r="AI121" t="n">
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>MARIA ROSAS DE MOSQUEIRA/MARIA ROSAS DE MOSQUEIRA</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK121" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ121" t="inlineStr">
+      <c r="AL121" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11821,10 +13031,20 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
-      <c r="AI122" t="n">
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>PRITE DIVINO NIÑO</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK122" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ122" t="inlineStr">
+      <c r="AL122" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -11915,10 +13135,20 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
-      <c r="AI123" t="n">
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK123" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ123" t="inlineStr">
+      <c r="AL123" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12007,10 +13237,20 @@
           <t>UGEL ATALAYA</t>
         </is>
       </c>
-      <c r="AI124" t="n">
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>ATALAYA/ATALAYA</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK124" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ124" t="inlineStr">
+      <c r="AL124" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12099,10 +13339,20 @@
           <t>UGEL SAN MARCOS</t>
         </is>
       </c>
-      <c r="AI125" t="n">
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>SAN MARCOS/SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK125" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ125" t="inlineStr">
+      <c r="AL125" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12191,10 +13441,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="AI126" t="n">
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>LUDWIG VAN BEETHOVEN/LUDWIG VAN BEETHOVEN</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK126" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ126" t="inlineStr">
+      <c r="AL126" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12285,10 +13545,20 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
-      <c r="AI127" t="n">
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>HELEN KELLER/HELEN KELLER</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK127" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ127" t="inlineStr">
+      <c r="AL127" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12377,10 +13647,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="AI128" t="n">
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>PRITE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK128" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ128" t="inlineStr">
+      <c r="AL128" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12471,10 +13751,20 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
-      <c r="AI129" t="n">
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>PRITE 01</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK129" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ129" t="inlineStr">
+      <c r="AL129" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12565,10 +13855,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="AI130" t="n">
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>PRITE LOS ANGELITOS</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK130" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ130" t="inlineStr">
+      <c r="AL130" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12657,10 +13957,20 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
-      <c r="AI131" t="n">
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>SANTA MARIA DE GUADALUPE/SANTA MARIA DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK131" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ131" t="inlineStr">
+      <c r="AL131" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12749,10 +14059,20 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
-      <c r="AI132" t="n">
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK132" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ132" t="inlineStr">
+      <c r="AL132" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12841,10 +14161,20 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
-      <c r="AI133" t="n">
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>SAN CLEMENTE/SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK133" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ133" t="inlineStr">
+      <c r="AL133" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -12933,10 +14263,20 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
-      <c r="AI134" t="n">
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>SAN PEDRO/SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK134" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ134" t="inlineStr">
+      <c r="AL134" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13027,10 +14367,20 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
-      <c r="AI135" t="n">
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>SOMOS DESCUBRIDORES/SOMOS DESCUBRIDORES</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK135" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ135" t="inlineStr">
+      <c r="AL135" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13121,10 +14471,20 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
-      <c r="AI136" t="n">
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>CIUDAD MAJES/CIUDAD MAJES</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK136" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ136" t="inlineStr">
+      <c r="AL136" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13213,10 +14573,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="AI137" t="n">
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>09 SANTA LUCIA/09 SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK137" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ137" t="inlineStr">
+      <c r="AL137" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13307,10 +14677,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="AI138" t="n">
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>MADRE TERESA DE CALCULTA/MADRE TERESA DE CALCULTA</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK138" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ138" t="inlineStr">
+      <c r="AL138" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13401,10 +14781,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="AI139" t="n">
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>SOLIDARIDAD/SOLIDARIDAD</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK139" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ139" t="inlineStr">
+      <c r="AL139" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13493,10 +14883,20 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
-      <c r="AI140" t="n">
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK140" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ140" t="inlineStr">
+      <c r="AL140" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13587,10 +14987,20 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
-      <c r="AI141" t="n">
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>PRITE VIRGEN MARIA</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK141" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ141" t="inlineStr">
+      <c r="AL141" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13681,10 +15091,20 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
-      <c r="AI142" t="n">
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>YAUYOS</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK142" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ142" t="inlineStr">
+      <c r="AL142" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13773,10 +15193,20 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
-      <c r="AI143" t="n">
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>NIÑO JESUS DE PRAGA/NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK143" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ143" t="inlineStr">
+      <c r="AL143" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13867,10 +15297,20 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
-      <c r="AI144" t="n">
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>NUESTRA SEÑORA DEL ROSARIO/PRITE NUESTRA SEÑORA DEL ROSARIO/NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK144" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ144" t="inlineStr">
+      <c r="AL144" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -13959,10 +15399,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="AI145" t="n">
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>PRITE ALEGRIA EN EL CORAZON II</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK145" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ145" t="inlineStr">
+      <c r="AL145" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14053,10 +15503,20 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
-      <c r="AI146" t="n">
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>MANUEL VILLAVICENCIO GARGATE/MANUEL VILLAVICENCIO GARGATE</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK146" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ146" t="inlineStr">
+      <c r="AL146" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14147,10 +15607,20 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
-      <c r="AI147" t="n">
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>9 DE OCTUBRE/9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK147" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ147" t="inlineStr">
+      <c r="AL147" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14239,10 +15709,20 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
-      <c r="AI148" t="n">
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>25507</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK148" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ148" t="inlineStr">
+      <c r="AL148" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14333,10 +15813,20 @@
           <t>UGEL JUNÍN</t>
         </is>
       </c>
-      <c r="AI149" t="n">
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>VIRGEN DE LAS NIEVES</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK149" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ149" t="inlineStr">
+      <c r="AL149" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14427,10 +15917,20 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
-      <c r="AI150" t="n">
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK150" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ150" t="inlineStr">
+      <c r="AL150" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14521,10 +16021,20 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
-      <c r="AI151" t="n">
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>JAVIER DIEZ CANSECO CISNEROS/JAVIER DIEZ CANSECO CISNEROS</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK151" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ151" t="inlineStr">
+      <c r="AL151" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14613,10 +16123,20 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
-      <c r="AI152" t="n">
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>AJUTAP</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK152" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ152" t="inlineStr">
+      <c r="AL152" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14707,10 +16227,20 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
-      <c r="AI153" t="n">
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>MI MUNDO FELIZ/MI MUNDO FELIZ</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK153" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ153" t="inlineStr">
+      <c r="AL153" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14801,10 +16331,20 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
-      <c r="AI154" t="n">
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>DIVINO TESORO/DIVINO TESORO</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK154" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ154" t="inlineStr">
+      <c r="AL154" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14893,10 +16433,20 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
-      <c r="AI155" t="n">
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>PRITE 04</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK155" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ155" t="inlineStr">
+      <c r="AL155" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -14987,10 +16537,20 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
-      <c r="AI156" t="n">
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>008 DIVINO NIÑO JESUS/008 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK156" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ156" t="inlineStr">
+      <c r="AL156" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15079,10 +16639,20 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
-      <c r="AI157" t="n">
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK157" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ157" t="inlineStr">
+      <c r="AL157" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15173,10 +16743,20 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
-      <c r="AI158" t="n">
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>FRANCISCO BOLOGNESI/PRITE MARCONA/FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK158" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ158" t="inlineStr">
+      <c r="AL158" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15265,10 +16845,20 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
-      <c r="AI159" t="n">
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>HUACCANA</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK159" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ159" t="inlineStr">
+      <c r="AL159" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15359,10 +16949,20 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
-      <c r="AI160" t="n">
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>PRITE VILLA DEL SALVADOR</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK160" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ160" t="inlineStr">
+      <c r="AL160" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15453,10 +17053,20 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
-      <c r="AI161" t="n">
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>ANGELES DE GLORIA</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK161" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ161" t="inlineStr">
+      <c r="AL161" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15545,10 +17155,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="AI162" t="n">
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>PRITE FRAY PEDRO URRACA</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK162" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ162" t="inlineStr">
+      <c r="AL162" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15639,10 +17259,20 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
-      <c r="AI163" t="n">
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>LA CENTRAL</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK163" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ163" t="inlineStr">
+      <c r="AL163" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15733,10 +17363,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="AI164" t="n">
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>PRITE HERMANO ANDRES</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK164" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ164" t="inlineStr">
+      <c r="AL164" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15825,10 +17465,20 @@
           <t>UGEL PARURO</t>
         </is>
       </c>
-      <c r="AI165" t="n">
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>PRITE NIÑO JESUS DE HUANOQUITE</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK165" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ165" t="inlineStr">
+      <c r="AL165" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -15919,10 +17569,20 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
-      <c r="AI166" t="n">
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>007 NUESTRO SEÑOR DE LOS MILAGROS/007 NUESTRO SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK166" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ166" t="inlineStr">
+      <c r="AL166" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16011,10 +17671,20 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
-      <c r="AI167" t="n">
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK167" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ167" t="inlineStr">
+      <c r="AL167" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16105,10 +17775,20 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
-      <c r="AI168" t="n">
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>LACHE/LACHE</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK168" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ168" t="inlineStr">
+      <c r="AL168" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16197,10 +17877,20 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
-      <c r="AI169" t="n">
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>PRITE MI LINDA CASITA</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK169" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ169" t="inlineStr">
+      <c r="AL169" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16289,10 +17979,20 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
-      <c r="AI170" t="n">
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>PRITE DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK170" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ170" t="inlineStr">
+      <c r="AL170" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16383,10 +18083,20 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
-      <c r="AI171" t="n">
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>PRITE ANGELITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK171" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ171" t="inlineStr">
+      <c r="AL171" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16475,10 +18185,20 @@
           <t>UGEL PUERTO BERMÚDEZ</t>
         </is>
       </c>
-      <c r="AI172" t="n">
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>PRITE PUERTO BERMUDEZ</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK172" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ172" t="inlineStr">
+      <c r="AL172" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>
@@ -16567,10 +18287,20 @@
           <t>UGEL PADRE ABAD</t>
         </is>
       </c>
-      <c r="AI173" t="n">
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK173" t="n">
         <v>2026</v>
       </c>
-      <c r="AJ173" t="inlineStr">
+      <c r="AL173" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_accesibilidad_2026.xlsx
@@ -419,137 +419,137 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Códigos modulares del local educativo</t>
+          <t>codigos_modulares_del_local_educativo</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Monto asignado total (S/)</t>
+          <t>monto_asignado_total_s</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Monto transferido (S/)</t>
+          <t>monto_transferido_s</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Estado de la Ficha de Acciones de Acondicionamiento (FAA)</t>
+          <t>estado_de_la_ficha_de_acciones_de_acondicionamiento_faa</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Acceso al local educativo y áreas exteriores</t>
+          <t>acceso_al_local_educativo_y_areas_exteriores</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Acceso a edificaciones</t>
+          <t>acceso_a_edificaciones</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Servicios higiénicos PRITE</t>
+          <t>servicios_higienicos_prite</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Servicios higiénicos CEBE</t>
+          <t>servicios_higienicos_cebe</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Servicios higiénicos de otras modalidades</t>
+          <t>servicios_higienicos_de_otras_modalidades</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Área de recreación accesibles</t>
+          <t>area_de_recreacion_accesibles</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Señalización</t>
+          <t>senalizacion</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Circulación vertical</t>
+          <t>circulacion_vertical</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Monto total de la FAA</t>
+          <t>monto_total_de_la_faa</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Estado de la Declaración de Gastos (DG)</t>
+          <t>estado_de_la_declaracion_de_gastos_dg</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Equipamiento</t>
+          <t>equipamiento</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Escaleras</t>
+          <t>escaleras</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Instalaciones sanitarias</t>
+          <t>instalaciones_sanitarias</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Muros / paneles (SS.HH.)</t>
+          <t>muros_paneles_ss_hh</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>pisos</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Puertas</t>
+          <t>puertas</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Rampas</t>
+          <t>rampas</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Señalización (1)</t>
+          <t>senalizacion_1</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Vegetación</t>
+          <t>vegetacion</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Monto total de la DG</t>
+          <t>monto_total_de_la_dg</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
